--- a/frontend/data/Kỹ thuật.xlsx
+++ b/frontend/data/Kỹ thuật.xlsx
@@ -1,93 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D3BAE9F-CC7B-4798-B856-4B758BA3CF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Tu luan 2 cot" sheetId="1" r:id="rId1"/>
+    <sheet name="Kỹ thuật" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>Câu hỏi</t>
-  </si>
-  <si>
-    <t>Đáp án mẫu</t>
-  </si>
-  <si>
-    <t>Đ/c cho biết Nội dung bảo quản VKTBKT hàng ngày? Thời gian?</t>
-  </si>
-  <si>
-    <t>"- Vũ khí bộ binh bảo quản 15 phút; vũ khí trang bị kỹ thuật, khí tài phức tạp bảo quản 30 phút, thời gian bảo quản vào giờ thứ 8.
-- Bảo quản hàng ngày do chiến sĩ được giao quản lý, sử dụng vũ khí trang bị kỹ thuật tiến hành bảo quản, bảo quản dưới sự phân công của chỉ huy đơn vị.
-* Nội dung bảo quản hàng ngày:
-- Trường hợp có sử dụng đến súng thì tháo thông thường để tiến hành lau:
-+ Lau sạch cát, bụi bẩn bên ngoài súng, trong nòng súng;
-+ Thông sạch nòng súng, lau sạch khóa nòng;
-+ Đối với súng cối 60mm, B41 ngoài những nội dung trên còn phải lau sạch giá súng, bộ phận tầm, hướng, hòm khẩu đội, kính ngắm quang học...
-+ Thông một lớp dầu mỏng vào lòng nòng súng và bôi một lớp dầu mỏng vào các bộ phận kim loại (không sơn).
-- Trường hợp trong ngày không sử dụng đến súng thì chỉ lau bên ngoài, sau đó bôi một lớp dầu mỏng lên các chi tiết bằng kim loại (không sơn)."</t>
-  </si>
-  <si>
-    <t>Đ/c cho biết Nội dung bảo quản VKTBKT hàng tuần ? Thời gian?</t>
-  </si>
-  <si>
-    <t>"trang bị kỹ thuật, khí tài phức tạp bảo quản từ 3-5 giờ; thời gian bảo quản vào ngày làm việc cuối tuần.
-- Bảo quản vũ khí trang bị kỹ thuật hàng tuần do Tiểu đoàn tổ chức, chiến sĩ được giao quản lý, sử dụng tiến hành bảo quản dưới sự phân công của chỉ huy trung đội, đại đội.
-- Nội dung: Ngoài những nội dung bảo quản ngày còn làm thêm những công việc sau:
-+ Hong phơi, khâu vá trang cụ, lau nòng dự bị dụng cụ phụ tùng.
-+ Lau chùi bên ngoài hòm hộp đạn rời.
-+ Vệ sinh, củng cố, sữa chữa các dụng cụ, phương tiện cất giữ."</t>
-  </si>
-  <si>
-    <t>Đ/c cho biết Tên của CVĐ50?</t>
-  </si>
-  <si>
-    <t>Tên của CVĐ50: Quản lý, khai thác vũ khí trang bị kỹ thuật tốt, bền, an toàn, tiết kiệm và an toàn giao thông.</t>
-  </si>
-  <si>
-    <t>Biên chế 1 trung đội BB hiện nay gồm bao nhiêu khẩu Trung liên?</t>
-  </si>
-  <si>
-    <t>3 khẩu</t>
-  </si>
-  <si>
-    <t>1 Tiểu đội BB hiện nay được biên chế bao nhiêu Khẩu AK?</t>
-  </si>
-  <si>
-    <t>6 khẩu</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -110,26 +64,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -454,68 +396,48 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="55.81640625" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D3"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Câu hỏi</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Phương án</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Đáp án đúng</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Câu trả lời</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="271.2" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
+        <v>(Nhập nội dung câu hỏi trắc nghiệm)</v>
+      </c>
+      <c r="B2" t="str" xml:space="preserve">
+        <v xml:space="preserve">A. Đáp án A_x000d_
+B. Đáp án B_x000d_
+C. Đáp án C_x000d_
+D. Đáp án D</v>
+      </c>
+      <c r="C2" t="str">
+        <v>A. Đáp án A</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="150" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="B7" s="1"/>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>(Nhập nội dung câu hỏi tự luận)</v>
+      </c>
+      <c r="D3" t="str">
+        <v>(Nhập đáp án mẫu — Enter để xuống dòng)</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:B1" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
   </ignoredErrors>
 </worksheet>
 </file>